--- a/dados/excel/secretaria_escolaridade.xlsx
+++ b/dados/excel/secretaria_escolaridade.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -807,10 +807,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>15275.01</v>
+        <v>16172.17</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>15275.01</v>
+        <v>16172.17</v>
       </c>
     </row>
     <row r="3">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20700.06</v>
+        <v>17176.9</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>22917.33</v>
+        <v>12995.13</v>
       </c>
     </row>
     <row r="4">
@@ -849,10 +849,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>10627.11</v>
+        <v>17301.37</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>10627.11</v>
+        <v>17301.37</v>
       </c>
     </row>
     <row r="5">
@@ -870,10 +870,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>3857.46</v>
+        <v>3857.45</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>3689.2</v>
+        <v>3689.19</v>
       </c>
     </row>
     <row r="6">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>4650.22</v>
+        <v>4696.67</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>4666.17</v>
+        <v>4713.39</v>
       </c>
     </row>
     <row r="7">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>5946.11</v>
+        <v>5958.85</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>4919.18</v>
+        <v>4899.18</v>
       </c>
     </row>
     <row r="8">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>9125.299999999999</v>
+        <v>8621.34</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>7876.4</v>
+        <v>7780.03</v>
       </c>
     </row>
     <row r="10">
@@ -975,7 +975,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>11807.27</v>
+        <v>11846.1</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>9218.959999999999</v>
@@ -1017,10 +1017,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>4214.87</v>
+        <v>2803.33</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>4214.87</v>
+        <v>2803.33</v>
       </c>
     </row>
     <row r="13">
@@ -1038,10 +1038,10 @@
         <v>57</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>5058.51</v>
+        <v>5191.76</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>4449.86</v>
+        <v>4522.24</v>
       </c>
     </row>
     <row r="14">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3347.23</v>
+        <v>2640.09</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1786.89</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="15">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>10327.55</v>
+        <v>10141.88</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>8694.92</v>
+        <v>8667.4</v>
       </c>
     </row>
     <row r="16">
@@ -1101,10 +1101,10 @@
         <v>29</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>12821.71</v>
+        <v>12901.84</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>11690.56</v>
+        <v>11767.49</v>
       </c>
     </row>
     <row r="17">
@@ -1122,10 +1122,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>12887.22</v>
+        <v>10613.4</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>11743.09</v>
+        <v>10793.89</v>
       </c>
     </row>
     <row r="18">
@@ -1164,10 +1164,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>6095.56</v>
+        <v>6068.04</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>6095.56</v>
+        <v>6068.04</v>
       </c>
     </row>
     <row r="20">
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>3924.42</v>
+        <v>3834.32</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>3752.65</v>
+        <v>3725.13</v>
       </c>
     </row>
     <row r="22">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>4802.81</v>
+        <v>7338.25</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>4542.15</v>
+        <v>5426.72</v>
       </c>
     </row>
     <row r="23">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1436</v>
+        <v>1471</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>4433.93</v>
+        <v>4401.26</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>4111.03</v>
+        <v>4131.87</v>
       </c>
     </row>
     <row r="24">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>566</v>
+        <v>618</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1857.47</v>
+        <v>2229.69</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>1084.8</v>
+        <v>1640.32</v>
       </c>
     </row>
     <row r="25">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>4537</v>
+        <v>4951</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>5938.47</v>
+        <v>6016.12</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>4681.02</v>
+        <v>4876.53</v>
       </c>
     </row>
     <row r="26">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1433</v>
+        <v>1472</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>14240.88</v>
+        <v>14045.38</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>13690.2</v>
+        <v>13626.09</v>
       </c>
     </row>
     <row r="27">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>21574.92</v>
+        <v>21152.78</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>18086.39</v>
+        <v>18589.1</v>
       </c>
     </row>
     <row r="28">
@@ -1353,10 +1353,10 @@
         <v>9</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>19960.77</v>
+        <v>19864.41</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>18275.27</v>
+        <v>18268.46</v>
       </c>
     </row>
     <row r="29">
@@ -1395,10 +1395,10 @@
         <v>37</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5455.35</v>
+        <v>7402.05</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4729.97</v>
+        <v>7060.9</v>
       </c>
     </row>
     <row r="31">
@@ -1416,10 +1416,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>5364.81</v>
+        <v>6113.54</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>6873.26</v>
+        <v>6845.74</v>
       </c>
     </row>
     <row r="32">
@@ -1437,10 +1437,10 @@
         <v>107</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>14606.68</v>
+        <v>15960.07</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>12394.74</v>
+        <v>14204.41</v>
       </c>
     </row>
     <row r="33">
@@ -1458,10 +1458,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>19331.08</v>
+        <v>22168.76</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>21706.52</v>
+        <v>24154.78</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>4673.2</v>
+        <v>4175.34</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>4449.86</v>
+        <v>4422.34</v>
       </c>
     </row>
     <row r="35">
@@ -1500,10 +1500,10 @@
         <v>27</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>12286.94</v>
+        <v>12051.49</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>11910.93</v>
+        <v>11780.05</v>
       </c>
     </row>
     <row r="36">
@@ -1521,10 +1521,10 @@
         <v>2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>25663.38</v>
+        <v>24379.1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>25663.38</v>
+        <v>24379.1</v>
       </c>
     </row>
     <row r="37">
@@ -1542,10 +1542,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>18732.58</v>
+        <v>20920.86</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>18732.58</v>
+        <v>20920.86</v>
       </c>
     </row>
     <row r="38">
@@ -1563,10 +1563,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>17023.27</v>
+        <v>17111.33</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>17023.27</v>
+        <v>17111.33</v>
       </c>
     </row>
     <row r="39">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>16215.53</v>
+        <v>482.56</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>15480.31</v>
+        <v>482.56</v>
       </c>
     </row>
     <row r="40">
@@ -1598,38 +1598,38 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>13115.54</v>
+        <v>13287.19</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>13115.54</v>
+        <v>15607.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>7107.16</v>
+        <v>10094.76</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>5991.48</v>
+        <v>10094.76</v>
       </c>
     </row>
     <row r="42">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>5453</v>
+        <v>7278.63</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>5194.79</v>
+        <v>7337.46</v>
       </c>
     </row>
     <row r="43">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>6554.27</v>
+        <v>5371.77</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>6963.26</v>
+        <v>5167.27</v>
       </c>
     </row>
     <row r="44">
@@ -1682,17 +1682,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1271</v>
+        <v>5</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>6432.24</v>
+        <v>6714.8</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>5862.93</v>
+        <v>6987.88</v>
       </c>
     </row>
     <row r="45">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>87</v>
+        <v>1277</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>4111.56</v>
+        <v>6429.72</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>2241.92</v>
+        <v>5936.39</v>
       </c>
     </row>
     <row r="46">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1088</v>
+        <v>84</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>14088.96</v>
+        <v>4372.16</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>12449.49</v>
+        <v>4117.9</v>
       </c>
     </row>
     <row r="47">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>298</v>
+        <v>1087</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>21752.82</v>
+        <v>14276.35</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>18303.12</v>
+        <v>12982.02</v>
       </c>
     </row>
     <row r="48">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>37</v>
+        <v>296</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>22605.64</v>
+        <v>21032.47</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>17777.25</v>
+        <v>18226.75</v>
       </c>
     </row>
     <row r="49">
@@ -1787,38 +1787,38 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>25290.8</v>
+        <v>20238.77</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>22607.84</v>
+        <v>16110.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>8096.89</v>
+        <v>25050.17</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7123.76</v>
+        <v>21624.54</v>
       </c>
     </row>
     <row r="51">
@@ -1829,17 +1829,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>6656.3</v>
+        <v>8831.110000000001</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>8156.04</v>
+        <v>8188.68</v>
       </c>
     </row>
     <row r="52">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>8363.059999999999</v>
+        <v>6668.94</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>8363.059999999999</v>
+        <v>8156.04</v>
       </c>
     </row>
     <row r="53">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5888.79</v>
+        <v>8349.32</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>5035.49</v>
+        <v>8349.32</v>
       </c>
     </row>
     <row r="54">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2157.87</v>
+        <v>5777.38</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>1084.8</v>
+        <v>5069.13</v>
       </c>
     </row>
     <row r="55">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>12744.54</v>
+        <v>2112.25</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>11771.7</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="56">
@@ -1934,38 +1934,38 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>16509.06</v>
+        <v>13323.34</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>10878.65</v>
+        <v>11925.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>5385.33</v>
+        <v>20563.25</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>5385.33</v>
+        <v>15935.77</v>
       </c>
     </row>
     <row r="58">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>4965.52</v>
+        <v>7806.07</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>4449.86</v>
+        <v>7806.07</v>
       </c>
     </row>
     <row r="59">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>1129.52</v>
+        <v>5609.02</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>1084.8</v>
+        <v>4861.99</v>
       </c>
     </row>
     <row r="60">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>21323.05</v>
+        <v>1040.26</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>12394.73</v>
+        <v>904.8</v>
       </c>
     </row>
     <row r="61">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>39787.17</v>
+        <v>22186.6</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>38932.51</v>
+        <v>14815.48</v>
       </c>
     </row>
     <row r="62">
@@ -2060,38 +2060,38 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>54058.52</v>
+        <v>39553.14</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>54058.52</v>
+        <v>39363.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>5488.74</v>
+        <v>47278.4</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>5743.46</v>
+        <v>47278.4</v>
       </c>
     </row>
     <row r="64">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>1072.48</v>
+        <v>5461.21</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>1084.8</v>
+        <v>5715.93</v>
       </c>
     </row>
     <row r="65">
@@ -2123,17 +2123,17 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>13606.98</v>
+        <v>1078.64</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>14235.71</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="66">
@@ -2144,38 +2144,38 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>17988.25</v>
+        <v>14924.36</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>17988.25</v>
+        <v>15361.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>3776.58</v>
+        <v>16358.95</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>3776.58</v>
+        <v>16358.95</v>
       </c>
     </row>
     <row r="68">
@@ -2186,17 +2186,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>5012.54</v>
+        <v>3776.58</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>5012.54</v>
+        <v>3776.58</v>
       </c>
     </row>
     <row r="69">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>7860.78</v>
+        <v>4688.8</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>7860.78</v>
+        <v>4688.8</v>
       </c>
     </row>
     <row r="70">
@@ -2228,17 +2228,17 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>5226.08</v>
+        <v>7609.86</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>4774.84</v>
+        <v>7609.86</v>
       </c>
     </row>
     <row r="71">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>2115.15</v>
+        <v>5236.19</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>1084.8</v>
+        <v>4729.01</v>
       </c>
     </row>
     <row r="72">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>11954.26</v>
+        <v>2231.54</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>8459.07</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="73">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>15343.84</v>
+        <v>11949.09</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>13942.3</v>
+        <v>10748.28</v>
       </c>
     </row>
     <row r="74">
@@ -2312,38 +2312,38 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>19215.13</v>
+        <v>13766.38</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>19215.13</v>
+        <v>11780.28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>1048.8</v>
+        <v>14261.19</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>1084.8</v>
+        <v>14261.19</v>
       </c>
     </row>
     <row r="76">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>15662.73</v>
+        <v>1048.8</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>15480.3</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>4405.8</v>
+        <v>14516.75</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>4449.86</v>
+        <v>15452.79</v>
       </c>
     </row>
     <row r="78">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>1084.8</v>
+        <v>5276.5</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>1084.8</v>
+        <v>4729.43</v>
       </c>
     </row>
     <row r="79">
@@ -2417,38 +2417,38 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>12911.39</v>
+        <v>1084.8</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>12362.42</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>5431.09</v>
+        <v>10909.84</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>4441.96</v>
+        <v>11459.79</v>
       </c>
     </row>
     <row r="81">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>6084.43</v>
+        <v>5203.38</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>5232.72</v>
+        <v>4041.97</v>
       </c>
     </row>
     <row r="82">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>1143.86</v>
+        <v>6360.43</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>1084.8</v>
+        <v>5087.09</v>
       </c>
     </row>
     <row r="83">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>12154.36</v>
+        <v>1087.38</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>10552.67</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="84">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>12744.03</v>
+        <v>11525.91</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>10893.15</v>
+        <v>9630.389999999999</v>
       </c>
     </row>
     <row r="85">
@@ -2543,38 +2543,38 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16765.09</v>
+        <v>12635.24</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>16765.09</v>
+        <v>11554</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>5225.42</v>
+        <v>16737.57</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>5042.32</v>
+        <v>16737.57</v>
       </c>
     </row>
     <row r="87">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1185.33</v>
+        <v>5222.4</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>1084.8</v>
+        <v>4810.41</v>
       </c>
     </row>
     <row r="88">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>13455.83</v>
+        <v>1130.19</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>12080.24</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="89">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>15464.3</v>
+        <v>14446.68</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>14213.6</v>
+        <v>12230.99</v>
       </c>
     </row>
     <row r="90">
@@ -2648,38 +2648,38 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>25715.13</v>
+        <v>17524.72</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>25715.13</v>
+        <v>14199.84</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>8065.2</v>
+        <v>25687.62</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>5562.2</v>
+        <v>25687.62</v>
       </c>
     </row>
     <row r="92">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1352.39</v>
+        <v>8003.49</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1084.8</v>
+        <v>5480.05</v>
       </c>
     </row>
     <row r="93">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>15021.67</v>
+        <v>1284.99</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>15480.31</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="94">
@@ -2732,38 +2732,38 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>26876.76</v>
+        <v>15860.35</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>20841.17</v>
+        <v>15452.79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>4449.86</v>
+        <v>31165.18</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>4449.86</v>
+        <v>18562.05</v>
       </c>
     </row>
     <row r="96">
@@ -2774,17 +2774,17 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>14707.52</v>
+        <v>4321.42</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>15480.31</v>
+        <v>4422.33</v>
       </c>
     </row>
     <row r="97">
@@ -2795,38 +2795,38 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>11932.33</v>
+        <v>12841.53</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>11932.33</v>
+        <v>11884.86</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>6615.11</v>
+        <v>13952.01</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>5632.41</v>
+        <v>13952.01</v>
       </c>
     </row>
     <row r="99">
@@ -2837,17 +2837,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>6807.12</v>
+        <v>5876.92</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>4990.65</v>
+        <v>5107.4</v>
       </c>
     </row>
     <row r="100">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>2686.23</v>
+        <v>6862.48</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>1084.8</v>
+        <v>4809.63</v>
       </c>
     </row>
     <row r="101">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>13215.48</v>
+        <v>2428.13</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>12807.17</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="102">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>16684.21</v>
+        <v>14226.9</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>16684.21</v>
+        <v>13931.5</v>
       </c>
     </row>
     <row r="103">
@@ -2921,38 +2921,38 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>21570.99</v>
+        <v>16739.25</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>21570.99</v>
+        <v>16739.25</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>8437.440000000001</v>
+        <v>21570.99</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>9947.559999999999</v>
+        <v>21570.99</v>
       </c>
     </row>
     <row r="105">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>1075.84</v>
+        <v>8675</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>1084.8</v>
+        <v>9933.790000000001</v>
       </c>
     </row>
     <row r="106">
@@ -2984,17 +2984,17 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>12384.8</v>
+        <v>1010.44</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>10333.88</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="107">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C107" s="12" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>16528.92</v>
+        <v>13609.47</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>17086.9</v>
+        <v>12139.08</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>5254.8</v>
+        <v>16437.51</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>5254.8</v>
+        <v>17151.78</v>
       </c>
     </row>
     <row r="109">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C109" s="12" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>7279.44</v>
+        <v>5339.38</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>6867.08</v>
+        <v>5339.38</v>
       </c>
     </row>
     <row r="110">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>1553.66</v>
+        <v>7570.31</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>1084.8</v>
+        <v>6634.31</v>
       </c>
     </row>
     <row r="111">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C111" s="12" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>12685.36</v>
+        <v>1454.47</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>11997.09</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="112">
@@ -3110,38 +3110,38 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>17524.17</v>
+        <v>12960.19</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>15845.35</v>
+        <v>11965.97</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C113" s="12" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>5764.12</v>
+        <v>16415.35</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>5240.32</v>
+        <v>14625.55</v>
       </c>
     </row>
     <row r="114">
@@ -3152,17 +3152,17 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>2649.31</v>
+        <v>5676.98</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>1084.8</v>
+        <v>5209.9</v>
       </c>
     </row>
     <row r="115">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C115" s="12" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>11614.17</v>
+        <v>2063.88</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>11550.11</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="116">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>20244.52</v>
+        <v>12235.19</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>13240.77</v>
+        <v>11843.06</v>
       </c>
     </row>
     <row r="117">
@@ -3215,38 +3215,38 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C117" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>15440.84</v>
+        <v>16189.35</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>15440.84</v>
+        <v>13319.43</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>15535.09</v>
+        <v>15440.84</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>16589.27</v>
+        <v>15440.84</v>
       </c>
     </row>
     <row r="119">
@@ -3257,38 +3257,38 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C119" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11826.88</v>
+        <v>24594.08</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>11826.88</v>
+        <v>16561.76</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>3712.9</v>
+        <v>13626.07</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>3712.9</v>
+        <v>13626.07</v>
       </c>
     </row>
     <row r="121">
@@ -3299,17 +3299,17 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C121" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>5397.47</v>
+        <v>3712.9</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>4544.22</v>
+        <v>3712.9</v>
       </c>
     </row>
     <row r="122">
@@ -3320,17 +3320,17 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>2819.19</v>
+        <v>4507.67</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>1084.8</v>
+        <v>4119.61</v>
       </c>
     </row>
     <row r="123">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C123" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>15207.44</v>
+        <v>2748.76</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>15163.21</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="124">
@@ -3362,38 +3362,38 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>6144.99</v>
+        <v>10880.56</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>6144.99</v>
+        <v>11065.98</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C125" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>6682.89</v>
+        <v>10958.06</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>6153.24</v>
+        <v>10958.06</v>
       </c>
     </row>
     <row r="126">
@@ -3404,17 +3404,17 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>11176.97</v>
+        <v>6669.13</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>12981.24</v>
+        <v>6139.48</v>
       </c>
     </row>
     <row r="127">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C127" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>11973.4</v>
+        <v>10288.41</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>13011.97</v>
+        <v>9883.51</v>
       </c>
     </row>
     <row r="128">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>8729.309999999999</v>
+        <v>11964.22</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>6706.7</v>
+        <v>12984.45</v>
       </c>
     </row>
     <row r="129">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C129" s="12" t="n">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>4336.42</v>
+        <v>8923.93</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>1084.8</v>
+        <v>6552.72</v>
       </c>
     </row>
     <row r="130">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>15117.62</v>
+        <v>4579.78</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>14605.11</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="131">
@@ -3509,38 +3509,38 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C131" s="12" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="D131" s="13" t="n">
-        <v>26075.42</v>
+        <v>15306.82</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>24923.17</v>
+        <v>14251.72</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>6335.1</v>
+        <v>25997.49</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>6335.1</v>
+        <v>24571.17</v>
       </c>
     </row>
     <row r="133">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C133" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D133" s="13" t="n">
-        <v>8438.08</v>
+        <v>6307.58</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>8748.41</v>
+        <v>6307.58</v>
       </c>
     </row>
     <row r="134">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>5027.86</v>
+        <v>7984.26</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>4557.24</v>
+        <v>8922.110000000001</v>
       </c>
     </row>
     <row r="135">
@@ -3593,17 +3593,17 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C135" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D135" s="13" t="n">
-        <v>4046.44</v>
+        <v>5052.73</v>
       </c>
       <c r="E135" s="13" t="n">
-        <v>4046.44</v>
+        <v>4786.45</v>
       </c>
     </row>
     <row r="136">
@@ -3614,17 +3614,17 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>5172.71</v>
+        <v>4224.54</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>4684.58</v>
+        <v>4224.54</v>
       </c>
     </row>
     <row r="137">
@@ -3635,17 +3635,17 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C137" s="12" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D137" s="13" t="n">
-        <v>8446.49</v>
+        <v>5317.31</v>
       </c>
       <c r="E137" s="13" t="n">
-        <v>8209.01</v>
+        <v>4883.2</v>
       </c>
     </row>
     <row r="138">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>13133.54</v>
+        <v>8111.12</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>12319.72</v>
+        <v>8240.01</v>
       </c>
     </row>
     <row r="139">
@@ -3677,17 +3677,17 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C139" s="12" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D139" s="13" t="n">
-        <v>16146.01</v>
+        <v>12304.81</v>
       </c>
       <c r="E139" s="13" t="n">
-        <v>14491.78</v>
+        <v>11620.69</v>
       </c>
     </row>
     <row r="140">
@@ -3698,38 +3698,38 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>17520.01</v>
+        <v>20120.19</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>17520.01</v>
+        <v>13856.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C141" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" s="13" t="n">
-        <v>4744.73</v>
+        <v>17589.04</v>
       </c>
       <c r="E141" s="13" t="n">
-        <v>4744.73</v>
+        <v>17589.04</v>
       </c>
     </row>
     <row r="142">
@@ -3740,17 +3740,17 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>985.36</v>
+        <v>4776.18</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1084.8</v>
+        <v>4776.18</v>
       </c>
     </row>
     <row r="143">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C143" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D143" s="13" t="n">
-        <v>15099.42</v>
+        <v>1188.6</v>
       </c>
       <c r="E143" s="13" t="n">
-        <v>15480.31</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="144">
@@ -3782,38 +3782,38 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>14601.37</v>
+        <v>15118.08</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>14601.37</v>
+        <v>15452.78</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C145" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D145" s="13" t="n">
-        <v>8073.06</v>
+        <v>13799.83</v>
       </c>
       <c r="E145" s="13" t="n">
-        <v>8073.06</v>
+        <v>13799.83</v>
       </c>
     </row>
     <row r="146">
@@ -3824,17 +3824,17 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>5368.18</v>
+        <v>8248.309999999999</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>5327.39</v>
+        <v>8248.309999999999</v>
       </c>
     </row>
     <row r="147">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C147" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D147" s="13" t="n">
-        <v>7474.66</v>
+        <v>5239.23</v>
       </c>
       <c r="E147" s="13" t="n">
-        <v>5138</v>
+        <v>5765.02</v>
       </c>
     </row>
     <row r="148">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>1707.78</v>
+        <v>6524.21</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>1084.8</v>
+        <v>5298.07</v>
       </c>
     </row>
     <row r="149">
@@ -3887,17 +3887,17 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C149" s="12" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="D149" s="13" t="n">
-        <v>12662.48</v>
+        <v>1537.99</v>
       </c>
       <c r="E149" s="13" t="n">
-        <v>11832.94</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="150">
@@ -3908,17 +3908,17 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>12201.77</v>
+        <v>12847.28</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>11905.76</v>
+        <v>11879.67</v>
       </c>
     </row>
     <row r="151">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C151" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D151" s="13" t="n">
-        <v>13844.22</v>
+        <v>11528.87</v>
       </c>
       <c r="E151" s="13" t="n">
-        <v>15025.92</v>
+        <v>13301.2</v>
       </c>
     </row>
     <row r="152">
@@ -3950,21 +3950,42 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>15010.07</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>16371.54</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
           <t>Doutorado</t>
         </is>
       </c>
-      <c r="C152" s="9" t="n">
+      <c r="C153" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D152" s="10" t="n">
-        <v>22976.76</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>22976.76</v>
+      <c r="D153" s="13" t="n">
+        <v>25459.73</v>
+      </c>
+      <c r="E153" s="13" t="n">
+        <v>25459.73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E152"/>
+  <autoFilter ref="A1:E153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>